--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.10_Q4_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.10_Q4_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.009806156983319823</v>
+        <v>0.009848785397729948</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009806156983319823</v>
+        <v>0.009848785397729948</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.009796298330423921</v>
+        <v>0.009837072391877229</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009796298330423921</v>
+        <v>0.009837072391877229</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.009777865568496224</v>
+        <v>0.009815162053796267</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009777865568496224</v>
+        <v>0.009815162053796267</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.009747956320731799</v>
+        <v>0.009780499381254939</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009747956320731799</v>
+        <v>0.009780499381254939</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.009710835358142612</v>
+        <v>0.009737662833087139</v>
       </c>
       <c r="C6" t="n">
-        <v>0.009710835358142612</v>
+        <v>0.009737662833087139</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.009666783363007931</v>
+        <v>0.009687199207192566</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009666783363007931</v>
+        <v>0.009687199207192566</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.009615358507952209</v>
+        <v>0.009627859646042973</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009615358507952209</v>
+        <v>0.009627859646042973</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.00956142538827625</v>
+        <v>0.009567124572499008</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00956142538827625</v>
+        <v>0.009567124572499008</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.009505183426248417</v>
+        <v>0.009504401702132804</v>
       </c>
       <c r="C10" t="n">
-        <v>0.009505183426248417</v>
+        <v>0.009504401702132804</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.009449298553108981</v>
+        <v>0.009442715485456003</v>
       </c>
       <c r="C11" t="n">
-        <v>0.009449298553108981</v>
+        <v>0.009442715485456003</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -595,10 +595,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.009395440802803886</v>
+        <v>0.009384824305664938</v>
       </c>
       <c r="C12" t="n">
-        <v>0.009395440802803886</v>
+        <v>0.009384824305664938</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.009347883160468853</v>
+        <v>0.009333533491039865</v>
       </c>
       <c r="C13" t="n">
-        <v>0.009347883160468853</v>
+        <v>0.009333533491039865</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.009307871855374695</v>
+        <v>0.009291203354227678</v>
       </c>
       <c r="C14" t="n">
-        <v>0.009307871855374695</v>
+        <v>0.009291203354227678</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -637,10 +637,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.009277168638706717</v>
+        <v>0.009259280252143294</v>
       </c>
       <c r="C15" t="n">
-        <v>0.009277168638706717</v>
+        <v>0.009259280252143294</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -651,10 +651,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.009257029125009317</v>
+        <v>0.009239513458070512</v>
       </c>
       <c r="C16" t="n">
-        <v>0.009257029125009317</v>
+        <v>0.009239513458070512</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.009250184848814772</v>
+        <v>0.009233757248449385</v>
       </c>
       <c r="C17" t="n">
-        <v>0.009250184848814772</v>
+        <v>0.009233757248449385</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.009257229576728837</v>
+        <v>0.009244196115766616</v>
       </c>
       <c r="C18" t="n">
-        <v>0.009257229576728837</v>
+        <v>0.009244196115766616</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.009281242543417141</v>
+        <v>0.009273157702000635</v>
       </c>
       <c r="C19" t="n">
-        <v>0.009281242543417141</v>
+        <v>0.009273157702000635</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -707,10 +707,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.009323459855965879</v>
+        <v>0.009322816403207005</v>
       </c>
       <c r="C20" t="n">
-        <v>0.009323459855965879</v>
+        <v>0.009322816403207005</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.009398043290170211</v>
+        <v>0.009405353171480127</v>
       </c>
       <c r="C21" t="n">
-        <v>0.009398043290170211</v>
+        <v>0.009405353171480127</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -735,10 +735,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.009490675603803718</v>
+        <v>0.009507757474054933</v>
       </c>
       <c r="C22" t="n">
-        <v>0.009490675603803718</v>
+        <v>0.009507757474054933</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -749,10 +749,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.009601508192151173</v>
+        <v>0.009630317478084904</v>
       </c>
       <c r="C23" t="n">
-        <v>0.009601508192151173</v>
+        <v>0.009630317478084904</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -763,10 +763,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.00974174863780124</v>
+        <v>0.009782329012501275</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00974174863780124</v>
+        <v>0.009782329012501275</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.009905545050356636</v>
+        <v>0.009959086181267361</v>
       </c>
       <c r="C25" t="n">
-        <v>0.009905545050356636</v>
+        <v>0.009959086181267361</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.01009806605076836</v>
+        <v>0.01016713834230292</v>
       </c>
       <c r="C26" t="n">
-        <v>0.01009806605076836</v>
+        <v>0.01016713834230292</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -805,10 +805,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.01032325541228491</v>
+        <v>0.01040896117798048</v>
       </c>
       <c r="C27" t="n">
-        <v>0.01032325541228491</v>
+        <v>0.01040896117798048</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -819,10 +819,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.01057890032775436</v>
+        <v>0.01068300604249499</v>
       </c>
       <c r="C28" t="n">
-        <v>0.01057890032775436</v>
+        <v>0.01068300604249499</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -833,10 +833,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.01086760820881124</v>
+        <v>0.01099077478313687</v>
       </c>
       <c r="C29" t="n">
-        <v>0.01086760820881124</v>
+        <v>0.01099077478313687</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -847,10 +847,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.01119016007429654</v>
+        <v>0.01133359075301788</v>
       </c>
       <c r="C30" t="n">
-        <v>0.01119016007429654</v>
+        <v>0.01133359075301788</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -861,10 +861,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.01154697888479223</v>
+        <v>0.01171215793348788</v>
       </c>
       <c r="C31" t="n">
-        <v>0.01154697888479223</v>
+        <v>0.01171215793348788</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
